--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260810.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>888,349</t>
+          <t>146,482</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>146,482</t>
+          <t>888,349</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,340,000</t>
+          <t>389,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>389,000</t>
+          <t>3,340,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,899,000</t>
+          <t>5,929,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,929,000</t>
+          <t>1,899,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>797,000</t>
+          <t>1,429,384</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,429,384</t>
+          <t>797,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>603,000</t>
+          <t>7,430,249</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,430,249</t>
+          <t>603,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>188,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>188,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>5,140,956</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>5,140,956</t>
+          <t>96,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>331,000</t>
+          <t>119,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>119,000</t>
+          <t>331,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,039,121</t>
+          <t>1,822,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,822,000</t>
+          <t>1,039,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>263,000</t>
+          <t>162,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>162,000</t>
+          <t>705,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>705,000</t>
+          <t>263,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
